--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/ValueSet-mii-vs-onko-marker-gene-hgnc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
